--- a/sletat-ru-mediaplan.xlsx
+++ b/sletat-ru-mediaplan.xlsx
@@ -436,11 +436,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -450,20 +450,19 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Медиаплан теста · Слетать.ру · Cerebro Click Out · Ozon Performance + Яндекс Urban Ads</t>
+          <t>Медиаплан теста · Слетать.ру · Ozon Performance · IV квартал 2026 · Cerebro Click Out</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Жёлтые ячейки — входные параметры, меняйте их: расчёт пересчитается автоматически. CPM/CTR — бенчмарки ваших сегментов из кабинетов площадок (Ozon — факт кабинета, Urban — расчёт до ответа площадки). WB Media недоступен (WB Тревел).</t>
+          <t>Жёлтые ячейки — входные параметры, меняйте их: расчёт пересчитается автоматически. CPM/CTR — бенчмарки ваших сегментов из кабинета Ozon. Urban Ads — второй шаг отдельным расчётом, WB Media недоступен (WB Тревел).</t>
         </is>
       </c>
     </row>
@@ -477,7 +476,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Бюджет на источник, ₽/мес</t>
+          <t>Медиабюджет Ozon Performance, ₽/мес</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -487,11 +486,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Сопровождение 2 источника, ₽/мес</t>
+          <t>Сопровождение 1 источник, ₽/мес</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>80000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="7">
@@ -527,7 +526,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Расчёт по сегментам (бюджет источника делится поровну между его сегментами)</t>
+          <t>Расчёт по сегментам (бюджет делится поровну между сегментами)</t>
         </is>
       </c>
     </row>
@@ -539,55 +538,50 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Источник</t>
+          <t>Бюджет, ₽</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Бюджет, ₽</t>
+          <t>CPM, ₽</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>CPM, ₽</t>
+          <t>CTR</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>CTR</t>
+          <t>Показы</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Показы</t>
+          <t>Охват (оценка)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Охват (оценка)</t>
+          <t>Клики</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Клики</t>
+          <t>CPC, ₽</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>CPC, ₽</t>
+          <t>Заявки</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Заявки</t>
+          <t>CPL медиа, ₽</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>CPL медиа, ₽</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Ёмкость: уникальных / мес</t>
         </is>
@@ -599,46 +593,41 @@
           <t>Ozon Travel + Путешествия (аксессуары)</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Ozon Performance</t>
-        </is>
-      </c>
-      <c r="C13" s="5">
+      <c r="B13" s="5">
         <f>$B$5/3</f>
         <v/>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="C13" s="6" t="n">
         <v>170</v>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="D13" s="7" t="n">
         <v>0.0023</v>
       </c>
+      <c r="E13" s="5">
+        <f>B13/C13*1000</f>
+        <v/>
+      </c>
       <c r="F13" s="5">
-        <f>C13/D13*1000</f>
+        <f>E13/$B$8</f>
         <v/>
       </c>
       <c r="G13" s="5">
-        <f>F13/$B$8</f>
+        <f>E13*D13</f>
         <v/>
       </c>
       <c r="H13" s="5">
-        <f>F13*E13</f>
+        <f>B13/G13</f>
         <v/>
       </c>
       <c r="I13" s="5">
-        <f>C13/H13</f>
+        <f>G13*$B$7</f>
         <v/>
       </c>
       <c r="J13" s="5">
-        <f>H13*$B$7</f>
-        <v/>
-      </c>
-      <c r="K13" s="5">
-        <f>C13/J13</f>
-        <v/>
-      </c>
-      <c r="L13" s="5" t="n">
+        <f>B13/I13</f>
+        <v/>
+      </c>
+      <c r="K13" s="5" t="n">
         <v>19458325</v>
       </c>
     </row>
@@ -648,46 +637,41 @@
           <t>Пляжная одежда + солнцезащита (сезон)</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Ozon Performance</t>
-        </is>
-      </c>
-      <c r="C14" s="5">
+      <c r="B14" s="5">
         <f>$B$5/3</f>
         <v/>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="C14" s="6" t="n">
         <v>143</v>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="D14" s="7" t="n">
         <v>0.0015</v>
       </c>
+      <c r="E14" s="5">
+        <f>B14/C14*1000</f>
+        <v/>
+      </c>
       <c r="F14" s="5">
-        <f>C14/D14*1000</f>
+        <f>E14/$B$8</f>
         <v/>
       </c>
       <c r="G14" s="5">
-        <f>F14/$B$8</f>
+        <f>E14*D14</f>
         <v/>
       </c>
       <c r="H14" s="5">
-        <f>F14*E14</f>
+        <f>B14/G14</f>
         <v/>
       </c>
       <c r="I14" s="5">
-        <f>C14/H14</f>
+        <f>G14*$B$7</f>
         <v/>
       </c>
       <c r="J14" s="5">
-        <f>H14*$B$7</f>
-        <v/>
-      </c>
-      <c r="K14" s="5">
-        <f>C14/J14</f>
-        <v/>
-      </c>
-      <c r="L14" s="5" t="n">
+        <f>B14/I14</f>
+        <v/>
+      </c>
+      <c r="K14" s="5" t="n">
         <v>7191660</v>
       </c>
     </row>
@@ -697,65 +681,64 @@
           <t>Широкая 25–55, города вылета</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Ozon Performance</t>
-        </is>
-      </c>
-      <c r="C15" s="5">
+      <c r="B15" s="5">
         <f>$B$5/3</f>
         <v/>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="C15" s="6" t="n">
         <v>144</v>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="D15" s="7" t="n">
         <v>0.0011</v>
       </c>
+      <c r="E15" s="5">
+        <f>B15/C15*1000</f>
+        <v/>
+      </c>
       <c r="F15" s="5">
-        <f>C15/D15*1000</f>
+        <f>E15/$B$8</f>
         <v/>
       </c>
       <c r="G15" s="5">
-        <f>F15/$B$8</f>
+        <f>E15*D15</f>
         <v/>
       </c>
       <c r="H15" s="5">
-        <f>F15*E15</f>
+        <f>B15/G15</f>
         <v/>
       </c>
       <c r="I15" s="5">
-        <f>C15/H15</f>
+        <f>G15*$B$7</f>
         <v/>
       </c>
       <c r="J15" s="5">
-        <f>H15*$B$7</f>
-        <v/>
-      </c>
-      <c r="K15" s="5">
-        <f>C15/J15</f>
-        <v/>
-      </c>
-      <c r="L15" s="5" t="n">
+        <f>B15/I15</f>
+        <v/>
+      </c>
+      <c r="K15" s="5" t="n">
         <v>21646162</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Итого Ozon Performance</t>
-        </is>
-      </c>
-      <c r="C16" s="8">
-        <f>SUM(C13:C15)</f>
-        <v/>
-      </c>
-      <c r="D16" s="5">
-        <f>C16/F16*1000</f>
-        <v/>
-      </c>
-      <c r="E16" s="9">
-        <f>H16/F16</f>
+          <t>Итого медиа Ozon Performance</t>
+        </is>
+      </c>
+      <c r="B16" s="8">
+        <f>SUM(B13:B15)</f>
+        <v/>
+      </c>
+      <c r="C16" s="5">
+        <f>B16/E16*1000</f>
+        <v/>
+      </c>
+      <c r="D16" s="9">
+        <f>G16/E16</f>
+        <v/>
+      </c>
+      <c r="E16" s="8">
+        <f>SUM(E13:E15)</f>
         <v/>
       </c>
       <c r="F16" s="8">
@@ -766,394 +749,162 @@
         <f>SUM(G13:G15)</f>
         <v/>
       </c>
-      <c r="H16" s="8">
-        <f>SUM(H13:H15)</f>
-        <v/>
-      </c>
-      <c r="I16" s="5">
-        <f>C16/H16</f>
-        <v/>
-      </c>
-      <c r="J16" s="8">
-        <f>SUM(J13:J15)</f>
-        <v/>
-      </c>
-      <c r="K16" s="5">
-        <f>C16/J16</f>
-        <v/>
-      </c>
-      <c r="L16" s="5" t="n"/>
+      <c r="H16" s="5">
+        <f>B16/G16</f>
+        <v/>
+      </c>
+      <c r="I16" s="8">
+        <f>SUM(I13:I15)</f>
+        <v/>
+      </c>
+      <c r="J16" s="5">
+        <f>B16/I16</f>
+        <v/>
+      </c>
+      <c r="K16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Чемоданы + путешествия-интересы</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Яндекс Urban Ads</t>
-        </is>
-      </c>
-      <c r="C17" s="5">
-        <f>$B$5/3</f>
-        <v/>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>268</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="F17" s="5">
-        <f>C17/D17*1000</f>
-        <v/>
-      </c>
-      <c r="G17" s="5">
-        <f>F17/$B$8</f>
-        <v/>
-      </c>
-      <c r="H17" s="5">
-        <f>F17*E17</f>
-        <v/>
-      </c>
-      <c r="I17" s="5">
-        <f>C17/H17</f>
-        <v/>
-      </c>
-      <c r="J17" s="5">
-        <f>H17*$B$7</f>
-        <v/>
-      </c>
-      <c r="K17" s="5">
-        <f>C17/J17</f>
-        <v/>
-      </c>
-      <c r="L17" s="5" t="n">
-        <v>14945220</v>
-      </c>
+          <t>Сопровождение</t>
+        </is>
+      </c>
+      <c r="B17" s="5">
+        <f>$B$6</f>
+        <v/>
+      </c>
+      <c r="C17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Семьи (прогулки и путешествия)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Яндекс Urban Ads</t>
-        </is>
-      </c>
-      <c r="C18" s="5">
-        <f>$B$5/3</f>
-        <v/>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>263</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="F18" s="5">
-        <f>C18/D18*1000</f>
-        <v/>
-      </c>
-      <c r="G18" s="5">
-        <f>F18/$B$8</f>
-        <v/>
-      </c>
-      <c r="H18" s="5">
-        <f>F18*E18</f>
-        <v/>
-      </c>
-      <c r="I18" s="5">
-        <f>C18/H18</f>
-        <v/>
-      </c>
-      <c r="J18" s="5">
-        <f>H18*$B$7</f>
-        <v/>
-      </c>
-      <c r="K18" s="5">
-        <f>C18/J18</f>
-        <v/>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v>7050460</v>
-      </c>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Итого в месяц</t>
+        </is>
+      </c>
+      <c r="B18" s="8">
+        <f>B16+B17</f>
+        <v/>
+      </c>
+      <c r="C18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Широкая, доход средний+</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Яндекс Urban Ads</t>
-        </is>
-      </c>
-      <c r="C19" s="5">
-        <f>$B$5/3</f>
-        <v/>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>255</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F19" s="5">
-        <f>C19/D19*1000</f>
-        <v/>
-      </c>
-      <c r="G19" s="5">
-        <f>F19/$B$8</f>
-        <v/>
-      </c>
-      <c r="H19" s="5">
-        <f>F19*E19</f>
-        <v/>
-      </c>
-      <c r="I19" s="5">
-        <f>C19/H19</f>
-        <v/>
-      </c>
-      <c r="J19" s="5">
-        <f>H19*$B$7</f>
-        <v/>
-      </c>
-      <c r="K19" s="5">
-        <f>C19/J19</f>
-        <v/>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v>9638770</v>
-      </c>
+          <t>CPC с сопровождением, ₽</t>
+        </is>
+      </c>
+      <c r="B19" s="5">
+        <f>B18/G16</f>
+        <v/>
+      </c>
+      <c r="C19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Итого Яндекс Urban Ads</t>
-        </is>
-      </c>
-      <c r="C20" s="8">
-        <f>SUM(C17:C19)</f>
-        <v/>
-      </c>
-      <c r="D20" s="5">
-        <f>C20/F20*1000</f>
-        <v/>
-      </c>
-      <c r="E20" s="9">
-        <f>H20/F20</f>
-        <v/>
-      </c>
-      <c r="F20" s="8">
-        <f>SUM(F17:F19)</f>
-        <v/>
-      </c>
-      <c r="G20" s="8">
-        <f>SUM(G17:G19)</f>
-        <v/>
-      </c>
-      <c r="H20" s="8">
-        <f>SUM(H17:H19)</f>
-        <v/>
-      </c>
-      <c r="I20" s="5">
-        <f>C20/H20</f>
-        <v/>
-      </c>
-      <c r="J20" s="8">
-        <f>SUM(J17:J19)</f>
-        <v/>
-      </c>
-      <c r="K20" s="5">
-        <f>C20/J20</f>
-        <v/>
-      </c>
-      <c r="L20" s="5" t="n"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CPL с сопровождением, ₽</t>
+        </is>
+      </c>
+      <c r="B20" s="5">
+        <f>B18/I16</f>
+        <v/>
+      </c>
+      <c r="C20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Итого медиа (два источника)</t>
-        </is>
-      </c>
-      <c r="C21" s="8">
-        <f>C16+C20</f>
-        <v/>
-      </c>
-      <c r="D21" s="5" t="n"/>
-      <c r="F21" s="8">
-        <f>F16+F20</f>
-        <v/>
-      </c>
-      <c r="G21" s="8">
-        <f>G16+G20</f>
-        <v/>
-      </c>
-      <c r="H21" s="8">
-        <f>H16+H20</f>
-        <v/>
-      </c>
-      <c r="I21" s="5">
-        <f>C21/H21</f>
-        <v/>
-      </c>
-      <c r="J21" s="8">
-        <f>J16+J20</f>
-        <v/>
-      </c>
-      <c r="K21" s="5">
-        <f>C21/J21</f>
-        <v/>
-      </c>
-      <c r="L21" s="5" t="n"/>
+          <t>Итого за срок теста, ₽</t>
+        </is>
+      </c>
+      <c r="B21" s="8">
+        <f>B18*$B$9</f>
+        <v/>
+      </c>
+      <c r="C21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Сопровождение</t>
-        </is>
-      </c>
-      <c r="C22" s="5">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="D22" s="5" t="n"/>
+          <t>Кликов за срок теста</t>
+        </is>
+      </c>
+      <c r="B22" s="5">
+        <f>G16*$B$9</f>
+        <v/>
+      </c>
+      <c r="C22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="5" t="n"/>
       <c r="H22" s="5" t="n"/>
       <c r="I22" s="5" t="n"/>
       <c r="J22" s="5" t="n"/>
       <c r="K22" s="5" t="n"/>
-      <c r="L22" s="5" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Итого в месяц</t>
-        </is>
-      </c>
-      <c r="C23" s="8">
-        <f>C21+C22</f>
-        <v/>
-      </c>
-      <c r="D23" s="5" t="n"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Заявок за срок теста</t>
+        </is>
+      </c>
+      <c r="B23" s="5">
+        <f>I16*$B$9</f>
+        <v/>
+      </c>
+      <c r="C23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n"/>
       <c r="G23" s="5" t="n"/>
       <c r="H23" s="5" t="n"/>
       <c r="I23" s="5" t="n"/>
       <c r="J23" s="5" t="n"/>
       <c r="K23" s="5" t="n"/>
-      <c r="L23" s="5" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>CPC с сопровождением, ₽</t>
-        </is>
-      </c>
-      <c r="C24" s="5">
-        <f>C23/H21</f>
-        <v/>
-      </c>
-      <c r="D24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="n"/>
-      <c r="L24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CPL с сопровождением, ₽</t>
-        </is>
-      </c>
-      <c r="C25" s="5">
-        <f>C23/J21</f>
-        <v/>
-      </c>
-      <c r="D25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="n"/>
-      <c r="L25" s="5" t="n"/>
+          <t>Условия: бюджет от 120 000 ₽/мес, контракт от 6 мес, тестовый период 8 недель, сопровождение 1 источника — 50 000 ₽/мес. Бонусные рубли по шкале Церебро — с расхода от 360 001 ₽/мес.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Итого за срок теста, ₽</t>
-        </is>
-      </c>
-      <c r="C26" s="8">
-        <f>C23*$B$9</f>
-        <v/>
-      </c>
-      <c r="D26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
-      <c r="L26" s="5" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Кликов за срок теста</t>
-        </is>
-      </c>
-      <c r="C27" s="5">
-        <f>H21*$B$9</f>
-        <v/>
-      </c>
-      <c r="D27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="n"/>
-      <c r="L27" s="5" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Заявок за срок теста</t>
-        </is>
-      </c>
-      <c r="C28" s="5">
-        <f>J21*$B$9</f>
-        <v/>
-      </c>
-      <c r="D28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="n"/>
-      <c r="L28" s="5" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Условия: бюджет от 120 000 ₽/мес на источник, контракт от 6 мес, тестовый период 8 недель. Сопровождение: 1 источник — 50 000, 2 — 80 000 ₽/мес (тестовый период).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Церебро Таргет · направление Click Out · clickout.cerebrotarget.ru</t>
         </is>

--- a/sletat-ru-mediaplan.xlsx
+++ b/sletat-ru-mediaplan.xlsx
@@ -60,12 +60,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -436,15 +437,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
@@ -462,7 +463,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Жёлтые ячейки — входные параметры, меняйте их: расчёт пересчитается автоматически. CPM/CTR — бенчмарки ваших сегментов из кабинета Ozon. Urban Ads — второй шаг отдельным расчётом, WB Media недоступен (WB Тревел).</t>
+          <t>Жёлтые ячейки — входные параметры, меняйте их: расчёт пересчитается автоматически. CPM/CTR — бенчмарки ваших сегментов из кабинета Ozon. Сопровождение — по шкале Церебро (см. блок «Шкала» ниже). Urban Ads — второй шаг отдельным расчётом, WB Media недоступен (WB Тревел).</t>
         </is>
       </c>
     </row>
@@ -472,6 +473,11 @@
           <t>Параметры</t>
         </is>
       </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Шкала сопровождения (СРК), доля от расхода</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -480,431 +486,551 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>200000</v>
+        <v>500000</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Расход до, ₽</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1-й месяц</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>со 2-го месяца (со скидкой)</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Сопровождение 1 источник, ₽/мес</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>50000</v>
+          <t>Конверсия клика в заявку</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D6" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>50 000 ₽</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>50 000 ₽</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Конверсия клика в заявку</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>0.015</v>
+          <t>Средняя частота показа (для охвата)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>360000</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Средняя частота показа (для охвата)</t>
+          <t>Срок теста, мес</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1099999</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Срок теста, мес</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>2</v>
+      <c r="D9" t="n">
+        <v>1999999</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="D10" t="n">
+        <v>6999999</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="D11" t="n">
+        <v>9999999</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>свыше</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Расчёт по сегментам (бюджет делится поровну между сегментами)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Сегмент</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Бюджет, ₽</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>CPM, ₽</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>CTR</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Показы</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Охват (оценка)</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Клики</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>CPC, ₽</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>Заявки</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>CPL медиа, ₽</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>Ёмкость: уникальных / мес</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Ozon Travel + Путешествия (аксессуары)</t>
         </is>
       </c>
-      <c r="B13" s="5">
+      <c r="B16" s="6">
         <f>$B$5/3</f>
         <v/>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C16" s="7" t="n">
         <v>170</v>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D16" s="8" t="n">
         <v>0.0023</v>
       </c>
-      <c r="E13" s="5">
-        <f>B13/C13*1000</f>
-        <v/>
-      </c>
-      <c r="F13" s="5">
-        <f>E13/$B$8</f>
-        <v/>
-      </c>
-      <c r="G13" s="5">
-        <f>E13*D13</f>
-        <v/>
-      </c>
-      <c r="H13" s="5">
-        <f>B13/G13</f>
-        <v/>
-      </c>
-      <c r="I13" s="5">
-        <f>G13*$B$7</f>
-        <v/>
-      </c>
-      <c r="J13" s="5">
-        <f>B13/I13</f>
-        <v/>
-      </c>
-      <c r="K13" s="5" t="n">
+      <c r="E16" s="6">
+        <f>B16/C16*1000</f>
+        <v/>
+      </c>
+      <c r="F16" s="6">
+        <f>E16/$B$7</f>
+        <v/>
+      </c>
+      <c r="G16" s="6">
+        <f>E16*D16</f>
+        <v/>
+      </c>
+      <c r="H16" s="6">
+        <f>B16/G16</f>
+        <v/>
+      </c>
+      <c r="I16" s="6">
+        <f>G16*$B$6</f>
+        <v/>
+      </c>
+      <c r="J16" s="6">
+        <f>B16/I16</f>
+        <v/>
+      </c>
+      <c r="K16" s="6" t="n">
         <v>19458325</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Пляжная одежда + солнцезащита (сезон)</t>
-        </is>
-      </c>
-      <c r="B14" s="5">
-        <f>$B$5/3</f>
-        <v/>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>143</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="E14" s="5">
-        <f>B14/C14*1000</f>
-        <v/>
-      </c>
-      <c r="F14" s="5">
-        <f>E14/$B$8</f>
-        <v/>
-      </c>
-      <c r="G14" s="5">
-        <f>E14*D14</f>
-        <v/>
-      </c>
-      <c r="H14" s="5">
-        <f>B14/G14</f>
-        <v/>
-      </c>
-      <c r="I14" s="5">
-        <f>G14*$B$7</f>
-        <v/>
-      </c>
-      <c r="J14" s="5">
-        <f>B14/I14</f>
-        <v/>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v>7191660</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Широкая 25–55, города вылета</t>
-        </is>
-      </c>
-      <c r="B15" s="5">
-        <f>$B$5/3</f>
-        <v/>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>144</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>0.0011</v>
-      </c>
-      <c r="E15" s="5">
-        <f>B15/C15*1000</f>
-        <v/>
-      </c>
-      <c r="F15" s="5">
-        <f>E15/$B$8</f>
-        <v/>
-      </c>
-      <c r="G15" s="5">
-        <f>E15*D15</f>
-        <v/>
-      </c>
-      <c r="H15" s="5">
-        <f>B15/G15</f>
-        <v/>
-      </c>
-      <c r="I15" s="5">
-        <f>G15*$B$7</f>
-        <v/>
-      </c>
-      <c r="J15" s="5">
-        <f>B15/I15</f>
-        <v/>
-      </c>
-      <c r="K15" s="5" t="n">
-        <v>21646162</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Итого медиа Ozon Performance</t>
-        </is>
-      </c>
-      <c r="B16" s="8">
-        <f>SUM(B13:B15)</f>
-        <v/>
-      </c>
-      <c r="C16" s="5">
-        <f>B16/E16*1000</f>
-        <v/>
-      </c>
-      <c r="D16" s="9">
-        <f>G16/E16</f>
-        <v/>
-      </c>
-      <c r="E16" s="8">
-        <f>SUM(E13:E15)</f>
-        <v/>
-      </c>
-      <c r="F16" s="8">
-        <f>SUM(F13:F15)</f>
-        <v/>
-      </c>
-      <c r="G16" s="8">
-        <f>SUM(G13:G15)</f>
-        <v/>
-      </c>
-      <c r="H16" s="5">
-        <f>B16/G16</f>
-        <v/>
-      </c>
-      <c r="I16" s="8">
-        <f>SUM(I13:I15)</f>
-        <v/>
-      </c>
-      <c r="J16" s="5">
-        <f>B16/I16</f>
-        <v/>
-      </c>
-      <c r="K16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Сопровождение</t>
-        </is>
-      </c>
-      <c r="B17" s="5">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="C17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="n"/>
+          <t>Пляжная одежда + солнцезащита (сезон)</t>
+        </is>
+      </c>
+      <c r="B17" s="6">
+        <f>$B$5/3</f>
+        <v/>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>143</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="E17" s="6">
+        <f>B17/C17*1000</f>
+        <v/>
+      </c>
+      <c r="F17" s="6">
+        <f>E17/$B$7</f>
+        <v/>
+      </c>
+      <c r="G17" s="6">
+        <f>E17*D17</f>
+        <v/>
+      </c>
+      <c r="H17" s="6">
+        <f>B17/G17</f>
+        <v/>
+      </c>
+      <c r="I17" s="6">
+        <f>G17*$B$6</f>
+        <v/>
+      </c>
+      <c r="J17" s="6">
+        <f>B17/I17</f>
+        <v/>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>7191660</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Итого в месяц</t>
-        </is>
-      </c>
-      <c r="B18" s="8">
-        <f>B16+B17</f>
-        <v/>
-      </c>
-      <c r="C18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Широкая 25–55, города вылета</t>
+        </is>
+      </c>
+      <c r="B18" s="6">
+        <f>$B$5/3</f>
+        <v/>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>144</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="E18" s="6">
+        <f>B18/C18*1000</f>
+        <v/>
+      </c>
+      <c r="F18" s="6">
+        <f>E18/$B$7</f>
+        <v/>
+      </c>
+      <c r="G18" s="6">
+        <f>E18*D18</f>
+        <v/>
+      </c>
+      <c r="H18" s="6">
+        <f>B18/G18</f>
+        <v/>
+      </c>
+      <c r="I18" s="6">
+        <f>G18*$B$6</f>
+        <v/>
+      </c>
+      <c r="J18" s="6">
+        <f>B18/I18</f>
+        <v/>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>21646162</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CPC с сопровождением, ₽</t>
-        </is>
-      </c>
-      <c r="B19" s="5">
-        <f>B18/G16</f>
-        <v/>
-      </c>
-      <c r="C19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Итого медиа Ozon Performance</t>
+        </is>
+      </c>
+      <c r="B19" s="9">
+        <f>SUM(B16:B18)</f>
+        <v/>
+      </c>
+      <c r="C19" s="6">
+        <f>B19/E19*1000</f>
+        <v/>
+      </c>
+      <c r="D19" s="10">
+        <f>G19/E19</f>
+        <v/>
+      </c>
+      <c r="E19" s="9">
+        <f>SUM(E16:E18)</f>
+        <v/>
+      </c>
+      <c r="F19" s="9">
+        <f>SUM(F16:F18)</f>
+        <v/>
+      </c>
+      <c r="G19" s="9">
+        <f>SUM(G16:G18)</f>
+        <v/>
+      </c>
+      <c r="H19" s="6">
+        <f>B19/G19</f>
+        <v/>
+      </c>
+      <c r="I19" s="9">
+        <f>SUM(I16:I18)</f>
+        <v/>
+      </c>
+      <c r="J19" s="6">
+        <f>B19/I19</f>
+        <v/>
+      </c>
+      <c r="K19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CPL с сопровождением, ₽</t>
-        </is>
-      </c>
-      <c r="B20" s="5">
-        <f>B18/I16</f>
-        <v/>
-      </c>
-      <c r="C20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="n"/>
+          <t>Сопровождение, 1-й месяц (по шкале)</t>
+        </is>
+      </c>
+      <c r="B20" s="6">
+        <f>IF($B$5&lt;=200000,50000,IF($B$5&lt;=360000,$B$5*0.2,$B$5*0.2))</f>
+        <v/>
+      </c>
+      <c r="C20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="6" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Итого за срок теста, ₽</t>
-        </is>
-      </c>
-      <c r="B21" s="8">
-        <f>B18*$B$9</f>
-        <v/>
-      </c>
-      <c r="C21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="n"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Сопровождение, со 2-го месяца (со скидкой)</t>
+        </is>
+      </c>
+      <c r="B21" s="6">
+        <f>IF($B$5&lt;=200000,50000,IF($B$5&lt;=360000,$B$5*0.2,IF($B$5&lt;=1099999,$B$5*0.1,IF($B$5&lt;=1999999,$B$5*0.08,IF($B$5&lt;=6999999,$B$5*0.06,IF($B$5&lt;=9999999,$B$5*0.04,$B$5*0.02))))))</f>
+        <v/>
+      </c>
+      <c r="C21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n"/>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Кликов за срок теста</t>
-        </is>
-      </c>
-      <c r="B22" s="5">
-        <f>G16*$B$9</f>
-        <v/>
-      </c>
-      <c r="C22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
+          <t>Итого в месяц, 1-й месяц</t>
+        </is>
+      </c>
+      <c r="B22" s="6">
+        <f>B19+B20</f>
+        <v/>
+      </c>
+      <c r="C22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Заявок за срок теста</t>
-        </is>
-      </c>
-      <c r="B23" s="5">
-        <f>I16*$B$9</f>
-        <v/>
-      </c>
-      <c r="C23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="n"/>
+          <t>Итого в месяц, со 2-го месяца</t>
+        </is>
+      </c>
+      <c r="B23" s="6">
+        <f>B19+B21</f>
+        <v/>
+      </c>
+      <c r="C23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CPC с сопровождением (со 2-го мес), ₽</t>
+        </is>
+      </c>
+      <c r="B24" s="6">
+        <f>B23/G19</f>
+        <v/>
+      </c>
+      <c r="C24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n"/>
+      <c r="J24" s="6" t="n"/>
+      <c r="K24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Условия: бюджет от 120 000 ₽/мес, контракт от 6 мес, тестовый период 8 недель, сопровождение 1 источника — 50 000 ₽/мес. Бонусные рубли по шкале Церебро — с расхода от 360 001 ₽/мес.</t>
-        </is>
-      </c>
+          <t>CPL с сопровождением (со 2-го мес), ₽</t>
+        </is>
+      </c>
+      <c r="B25" s="6">
+        <f>B23/I19</f>
+        <v/>
+      </c>
+      <c r="C25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="n"/>
+      <c r="J25" s="6" t="n"/>
+      <c r="K25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
+        <is>
+          <t>Итого за срок теста, ₽</t>
+        </is>
+      </c>
+      <c r="B26" s="6">
+        <f>B22+B23*($B$8-1)</f>
+        <v/>
+      </c>
+      <c r="C26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
+      <c r="J26" s="6" t="n"/>
+      <c r="K26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Кликов за срок теста</t>
+        </is>
+      </c>
+      <c r="B27" s="6">
+        <f>G19*$B$8</f>
+        <v/>
+      </c>
+      <c r="C27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n"/>
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Заявок за срок теста</t>
+        </is>
+      </c>
+      <c r="B28" s="6">
+        <f>I19*$B$8</f>
+        <v/>
+      </c>
+      <c r="C28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n"/>
+      <c r="J28" s="6" t="n"/>
+      <c r="K28" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Условия: контракт от 6 мес, тестовый период 8 недель. Оговорённый тестовый бюджет — 500 000 ₽/мес, может быть меньше (ниже 360 001 ₽ сопровождение 20% без скидки).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Церебро Таргет · направление Click Out · clickout.cerebrotarget.ru</t>
         </is>

--- a/sletat-ru-mediaplan.xlsx
+++ b/sletat-ru-mediaplan.xlsx
@@ -475,7 +475,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Шкала сопровождения (СРК), доля от расхода</t>
+          <t>Шкала сопровождения, доля от расхода</t>
         </is>
       </c>
     </row>

--- a/sletat-ru-mediaplan.xlsx
+++ b/sletat-ru-mediaplan.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Медиаплан" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Мотивация" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1039,4 +1040,329 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Скидка на сопровождение от рекламного оборота · шкала Церебро</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Жёлтая колонка — расход в месяц, меняйте: ставки и суммы пересчитаются. Первый месяц — 20%, со второго — ставка ступени при соблюдении её порога в предыдущем месяце.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Расход в месяц, ₽</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Сценарий</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Ставка без скидки</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Ставка со скидкой</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Сопровождение без скидки, ₽</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Со скидкой, ₽</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Экономия в месяц, ₽</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Экономия за 11 мес, ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n">
+        <v>350000</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Сокращённый тест</t>
+        </is>
+      </c>
+      <c r="C5" s="5">
+        <f>E5/A5</f>
+        <v/>
+      </c>
+      <c r="D5" s="5">
+        <f>F5/A5</f>
+        <v/>
+      </c>
+      <c r="E5" s="6">
+        <f>IF(A5&lt;=200000,50000,A5*0.2)</f>
+        <v/>
+      </c>
+      <c r="F5" s="6">
+        <f>IF(A5&lt;=200000,50000,IF(A5&lt;=360000,A5*0.2,IF(A5&lt;=1099999,A5*0.1,IF(A5&lt;=1999999,A5*0.08,IF(A5&lt;=6999999,A5*0.06,IF(A5&lt;=9999999,A5*0.04,A5*0.02))))))</f>
+        <v/>
+      </c>
+      <c r="G5" s="6">
+        <f>E5-F5</f>
+        <v/>
+      </c>
+      <c r="H5" s="6">
+        <f>G5*11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>500000</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Оговорённый тест</t>
+        </is>
+      </c>
+      <c r="C6" s="5">
+        <f>E6/A6</f>
+        <v/>
+      </c>
+      <c r="D6" s="5">
+        <f>F6/A6</f>
+        <v/>
+      </c>
+      <c r="E6" s="6">
+        <f>IF(A6&lt;=200000,50000,A6*0.2)</f>
+        <v/>
+      </c>
+      <c r="F6" s="6">
+        <f>IF(A6&lt;=200000,50000,IF(A6&lt;=360000,A6*0.2,IF(A6&lt;=1099999,A6*0.1,IF(A6&lt;=1999999,A6*0.08,IF(A6&lt;=6999999,A6*0.06,IF(A6&lt;=9999999,A6*0.04,A6*0.02))))))</f>
+        <v/>
+      </c>
+      <c r="G6" s="6">
+        <f>E6-F6</f>
+        <v/>
+      </c>
+      <c r="H6" s="6">
+        <f>G6*11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n">
+        <v>750000</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Расширение после теста</t>
+        </is>
+      </c>
+      <c r="C7" s="5">
+        <f>E7/A7</f>
+        <v/>
+      </c>
+      <c r="D7" s="5">
+        <f>F7/A7</f>
+        <v/>
+      </c>
+      <c r="E7" s="6">
+        <f>IF(A7&lt;=200000,50000,A7*0.2)</f>
+        <v/>
+      </c>
+      <c r="F7" s="6">
+        <f>IF(A7&lt;=200000,50000,IF(A7&lt;=360000,A7*0.2,IF(A7&lt;=1099999,A7*0.1,IF(A7&lt;=1999999,A7*0.08,IF(A7&lt;=6999999,A7*0.06,IF(A7&lt;=9999999,A7*0.04,A7*0.02))))))</f>
+        <v/>
+      </c>
+      <c r="G7" s="6">
+        <f>E7-F7</f>
+        <v/>
+      </c>
+      <c r="H7" s="6">
+        <f>G7*11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Рост: вторая ступень шкалы</t>
+        </is>
+      </c>
+      <c r="C8" s="5">
+        <f>E8/A8</f>
+        <v/>
+      </c>
+      <c r="D8" s="5">
+        <f>F8/A8</f>
+        <v/>
+      </c>
+      <c r="E8" s="6">
+        <f>IF(A8&lt;=200000,50000,A8*0.2)</f>
+        <v/>
+      </c>
+      <c r="F8" s="6">
+        <f>IF(A8&lt;=200000,50000,IF(A8&lt;=360000,A8*0.2,IF(A8&lt;=1099999,A8*0.1,IF(A8&lt;=1999999,A8*0.08,IF(A8&lt;=6999999,A8*0.06,IF(A8&lt;=9999999,A8*0.04,A8*0.02))))))</f>
+        <v/>
+      </c>
+      <c r="G8" s="6">
+        <f>E8-F8</f>
+        <v/>
+      </c>
+      <c r="H8" s="6">
+        <f>G8*11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Федеральный флайт</t>
+        </is>
+      </c>
+      <c r="C9" s="5">
+        <f>E9/A9</f>
+        <v/>
+      </c>
+      <c r="D9" s="5">
+        <f>F9/A9</f>
+        <v/>
+      </c>
+      <c r="E9" s="6">
+        <f>IF(A9&lt;=200000,50000,A9*0.2)</f>
+        <v/>
+      </c>
+      <c r="F9" s="6">
+        <f>IF(A9&lt;=200000,50000,IF(A9&lt;=360000,A9*0.2,IF(A9&lt;=1099999,A9*0.1,IF(A9&lt;=1999999,A9*0.08,IF(A9&lt;=6999999,A9*0.06,IF(A9&lt;=9999999,A9*0.04,A9*0.02))))))</f>
+        <v/>
+      </c>
+      <c r="G9" s="6">
+        <f>E9-F9</f>
+        <v/>
+      </c>
+      <c r="H9" s="6">
+        <f>G9*11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Сеть 350+ офисов, все источники</t>
+        </is>
+      </c>
+      <c r="C10" s="5">
+        <f>E10/A10</f>
+        <v/>
+      </c>
+      <c r="D10" s="5">
+        <f>F10/A10</f>
+        <v/>
+      </c>
+      <c r="E10" s="6">
+        <f>IF(A10&lt;=200000,50000,A10*0.2)</f>
+        <v/>
+      </c>
+      <c r="F10" s="6">
+        <f>IF(A10&lt;=200000,50000,IF(A10&lt;=360000,A10*0.2,IF(A10&lt;=1099999,A10*0.1,IF(A10&lt;=1999999,A10*0.08,IF(A10&lt;=6999999,A10*0.06,IF(A10&lt;=9999999,A10*0.04,A10*0.02))))))</f>
+        <v/>
+      </c>
+      <c r="G10" s="6">
+        <f>E10-F10</f>
+        <v/>
+      </c>
+      <c r="H10" s="6">
+        <f>G10*11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Верхняя ступень шкалы</t>
+        </is>
+      </c>
+      <c r="C11" s="5">
+        <f>E11/A11</f>
+        <v/>
+      </c>
+      <c r="D11" s="5">
+        <f>F11/A11</f>
+        <v/>
+      </c>
+      <c r="E11" s="6">
+        <f>IF(A11&lt;=200000,50000,A11*0.2)</f>
+        <v/>
+      </c>
+      <c r="F11" s="6">
+        <f>IF(A11&lt;=200000,50000,IF(A11&lt;=360000,A11*0.2,IF(A11&lt;=1099999,A11*0.1,IF(A11&lt;=1999999,A11*0.08,IF(A11&lt;=6999999,A11*0.06,IF(A11&lt;=9999999,A11*0.04,A11*0.02))))))</f>
+        <v/>
+      </c>
+      <c r="G11" s="6">
+        <f>E11-F11</f>
+        <v/>
+      </c>
+      <c r="H11" s="6">
+        <f>G11*11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Расход указан без НДС, стоимость сопровождения — с НДС. При сопровождении бонусные рубли не начисляются — действует только скидка.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/sletat-ru-mediaplan.xlsx
+++ b/sletat-ru-mediaplan.xlsx
@@ -464,7 +464,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Жёлтые ячейки — входные параметры, меняйте их: расчёт пересчитается автоматически. CPM/CTR — бенчмарки ваших сегментов из кабинета Ozon. Сопровождение — по шкале Церебро (см. блок «Шкала» ниже). Urban Ads — второй шаг отдельным расчётом, WB Media недоступен (WB Тревел).</t>
+          <t>Жёлтые ячейки — входные параметры, меняйте их: расчёт пересчитается автоматически. CPM/CTR — бенчмарки ваших сегментов из кабинета Ozon. Сопровождение — 10%, не менее 50 000 ₽ (см. блок «Шкала» ниже). Urban Ads — второй шаг отдельным расчётом, WB Media недоступен (WB Тревел).</t>
         </is>
       </c>
     </row>
@@ -496,12 +496,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1-й месяц</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>со 2-го месяца (со скидкой)</t>
+          <t>Ставка</t>
         </is>
       </c>
     </row>
@@ -515,16 +510,11 @@
         <v>0.015</v>
       </c>
       <c r="D6" t="n">
-        <v>200000</v>
+        <v>1099999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>50 000 ₽</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>50 000 ₽</t>
+          <t>10%, не менее 50 000 ₽</t>
         </is>
       </c>
     </row>
@@ -538,13 +528,10 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>360000</v>
+        <v>1999999</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="8">
@@ -557,58 +544,27 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>1099999</v>
+        <v>6999999</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="9">
       <c r="D9" t="n">
-        <v>1999999</v>
+        <v>9999999</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="10">
-      <c r="D10" t="n">
-        <v>6999999</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>свыше</t>
+        </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="D11" t="n">
-        <v>9999999</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>свыше</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F12" s="5" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -855,11 +811,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Сопровождение, 1-й месяц (по шкале)</t>
+          <t>Сопровождение (10%, не менее 50 000 ₽)</t>
         </is>
       </c>
       <c r="B20" s="6">
-        <f>IF($B$5&lt;=200000,50000,IF($B$5&lt;=360000,$B$5*0.2,$B$5*0.2))</f>
+        <f>IF($B$5&lt;=1099999,MAX($B$5*0.1,50000),IF($B$5&lt;=1999999,$B$5*0.08,IF($B$5&lt;=6999999,$B$5*0.06,IF($B$5&lt;=9999999,$B$5*0.04,$B$5*0.02))))</f>
         <v/>
       </c>
       <c r="C20" s="6" t="n"/>
@@ -874,11 +830,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Сопровождение, со 2-го месяца (со скидкой)</t>
+          <t>Сопровождение, со 2-го месяца (та же ставка)</t>
         </is>
       </c>
       <c r="B21" s="6">
-        <f>IF($B$5&lt;=200000,50000,IF($B$5&lt;=360000,$B$5*0.2,IF($B$5&lt;=1099999,$B$5*0.1,IF($B$5&lt;=1999999,$B$5*0.08,IF($B$5&lt;=6999999,$B$5*0.06,IF($B$5&lt;=9999999,$B$5*0.04,$B$5*0.02))))))</f>
+        <f>IF($B$5&lt;=1099999,MAX($B$5*0.1,50000),IF($B$5&lt;=1999999,$B$5*0.08,IF($B$5&lt;=6999999,$B$5*0.06,IF($B$5&lt;=9999999,$B$5*0.04,$B$5*0.02))))</f>
         <v/>
       </c>
       <c r="C21" s="6" t="n"/>
@@ -1026,7 +982,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Условия: контракт от 6 мес, тестовый период 8 недель. Оговорённый тестовый бюджет — 500 000 ₽/мес, может быть меньше (ниже 360 001 ₽ сопровождение 20% без скидки).</t>
+          <t>Условия: контракт от 6 мес, тестовый период 8 недель. Оговорённый тестовый бюджет — 500 000 ₽/мес, может быть меньше (сопровождение не менее 50 000 ₽/мес).</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1027,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Жёлтая колонка — расход в месяц, меняйте: ставки и суммы пересчитаются. Первый месяц — 20%, со второго — ставка ступени при соблюдении её порога в предыдущем месяце.</t>
+          <t>Жёлтая колонка — расход в месяц, меняйте: ставки и суммы пересчитаются. Базовая ставка 10%, не менее 50 000 ₽; от 1,1 млн — 8%, от 2 млн — 6%, от 7 млн — 4%, от 10 млн — 2%.</t>
         </is>
       </c>
     </row>
@@ -1088,22 +1044,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Ставка без скидки</t>
+          <t>Базовая ставка 10%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Ставка со скидкой</t>
+          <t>Ставка ступени</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Сопровождение без скидки, ₽</t>
+          <t>Сопровождение по базовой, ₽</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Со скидкой, ₽</t>
+          <t>По ставке ступени, ₽</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1113,7 +1069,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Экономия за 11 мес, ₽</t>
+          <t>Экономия за 12 мес, ₽</t>
         </is>
       </c>
     </row>
@@ -1135,11 +1091,11 @@
         <v/>
       </c>
       <c r="E5" s="6">
-        <f>IF(A5&lt;=200000,50000,A5*0.2)</f>
+        <f>MAX(A5*0.1,50000)</f>
         <v/>
       </c>
       <c r="F5" s="6">
-        <f>IF(A5&lt;=200000,50000,IF(A5&lt;=360000,A5*0.2,IF(A5&lt;=1099999,A5*0.1,IF(A5&lt;=1999999,A5*0.08,IF(A5&lt;=6999999,A5*0.06,IF(A5&lt;=9999999,A5*0.04,A5*0.02))))))</f>
+        <f>IF(A5&lt;=1099999,MAX(A5*0.1,50000),IF(A5&lt;=1999999,A5*0.08,IF(A5&lt;=6999999,A5*0.06,IF(A5&lt;=9999999,A5*0.04,A5*0.02))))</f>
         <v/>
       </c>
       <c r="G5" s="6">
@@ -1147,7 +1103,7 @@
         <v/>
       </c>
       <c r="H5" s="6">
-        <f>G5*11</f>
+        <f>G5*12</f>
         <v/>
       </c>
     </row>
@@ -1169,11 +1125,11 @@
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>IF(A6&lt;=200000,50000,A6*0.2)</f>
+        <f>MAX(A6*0.1,50000)</f>
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>IF(A6&lt;=200000,50000,IF(A6&lt;=360000,A6*0.2,IF(A6&lt;=1099999,A6*0.1,IF(A6&lt;=1999999,A6*0.08,IF(A6&lt;=6999999,A6*0.06,IF(A6&lt;=9999999,A6*0.04,A6*0.02))))))</f>
+        <f>IF(A6&lt;=1099999,MAX(A6*0.1,50000),IF(A6&lt;=1999999,A6*0.08,IF(A6&lt;=6999999,A6*0.06,IF(A6&lt;=9999999,A6*0.04,A6*0.02))))</f>
         <v/>
       </c>
       <c r="G6" s="6">
@@ -1181,7 +1137,7 @@
         <v/>
       </c>
       <c r="H6" s="6">
-        <f>G6*11</f>
+        <f>G6*12</f>
         <v/>
       </c>
     </row>
@@ -1203,11 +1159,11 @@
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>IF(A7&lt;=200000,50000,A7*0.2)</f>
+        <f>MAX(A7*0.1,50000)</f>
         <v/>
       </c>
       <c r="F7" s="6">
-        <f>IF(A7&lt;=200000,50000,IF(A7&lt;=360000,A7*0.2,IF(A7&lt;=1099999,A7*0.1,IF(A7&lt;=1999999,A7*0.08,IF(A7&lt;=6999999,A7*0.06,IF(A7&lt;=9999999,A7*0.04,A7*0.02))))))</f>
+        <f>IF(A7&lt;=1099999,MAX(A7*0.1,50000),IF(A7&lt;=1999999,A7*0.08,IF(A7&lt;=6999999,A7*0.06,IF(A7&lt;=9999999,A7*0.04,A7*0.02))))</f>
         <v/>
       </c>
       <c r="G7" s="6">
@@ -1215,7 +1171,7 @@
         <v/>
       </c>
       <c r="H7" s="6">
-        <f>G7*11</f>
+        <f>G7*12</f>
         <v/>
       </c>
     </row>
@@ -1237,11 +1193,11 @@
         <v/>
       </c>
       <c r="E8" s="6">
-        <f>IF(A8&lt;=200000,50000,A8*0.2)</f>
+        <f>MAX(A8*0.1,50000)</f>
         <v/>
       </c>
       <c r="F8" s="6">
-        <f>IF(A8&lt;=200000,50000,IF(A8&lt;=360000,A8*0.2,IF(A8&lt;=1099999,A8*0.1,IF(A8&lt;=1999999,A8*0.08,IF(A8&lt;=6999999,A8*0.06,IF(A8&lt;=9999999,A8*0.04,A8*0.02))))))</f>
+        <f>IF(A8&lt;=1099999,MAX(A8*0.1,50000),IF(A8&lt;=1999999,A8*0.08,IF(A8&lt;=6999999,A8*0.06,IF(A8&lt;=9999999,A8*0.04,A8*0.02))))</f>
         <v/>
       </c>
       <c r="G8" s="6">
@@ -1249,7 +1205,7 @@
         <v/>
       </c>
       <c r="H8" s="6">
-        <f>G8*11</f>
+        <f>G8*12</f>
         <v/>
       </c>
     </row>
@@ -1271,11 +1227,11 @@
         <v/>
       </c>
       <c r="E9" s="6">
-        <f>IF(A9&lt;=200000,50000,A9*0.2)</f>
+        <f>MAX(A9*0.1,50000)</f>
         <v/>
       </c>
       <c r="F9" s="6">
-        <f>IF(A9&lt;=200000,50000,IF(A9&lt;=360000,A9*0.2,IF(A9&lt;=1099999,A9*0.1,IF(A9&lt;=1999999,A9*0.08,IF(A9&lt;=6999999,A9*0.06,IF(A9&lt;=9999999,A9*0.04,A9*0.02))))))</f>
+        <f>IF(A9&lt;=1099999,MAX(A9*0.1,50000),IF(A9&lt;=1999999,A9*0.08,IF(A9&lt;=6999999,A9*0.06,IF(A9&lt;=9999999,A9*0.04,A9*0.02))))</f>
         <v/>
       </c>
       <c r="G9" s="6">
@@ -1283,7 +1239,7 @@
         <v/>
       </c>
       <c r="H9" s="6">
-        <f>G9*11</f>
+        <f>G9*12</f>
         <v/>
       </c>
     </row>
@@ -1305,11 +1261,11 @@
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>IF(A10&lt;=200000,50000,A10*0.2)</f>
+        <f>MAX(A10*0.1,50000)</f>
         <v/>
       </c>
       <c r="F10" s="6">
-        <f>IF(A10&lt;=200000,50000,IF(A10&lt;=360000,A10*0.2,IF(A10&lt;=1099999,A10*0.1,IF(A10&lt;=1999999,A10*0.08,IF(A10&lt;=6999999,A10*0.06,IF(A10&lt;=9999999,A10*0.04,A10*0.02))))))</f>
+        <f>IF(A10&lt;=1099999,MAX(A10*0.1,50000),IF(A10&lt;=1999999,A10*0.08,IF(A10&lt;=6999999,A10*0.06,IF(A10&lt;=9999999,A10*0.04,A10*0.02))))</f>
         <v/>
       </c>
       <c r="G10" s="6">
@@ -1317,7 +1273,7 @@
         <v/>
       </c>
       <c r="H10" s="6">
-        <f>G10*11</f>
+        <f>G10*12</f>
         <v/>
       </c>
     </row>
@@ -1339,11 +1295,11 @@
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>IF(A11&lt;=200000,50000,A11*0.2)</f>
+        <f>MAX(A11*0.1,50000)</f>
         <v/>
       </c>
       <c r="F11" s="6">
-        <f>IF(A11&lt;=200000,50000,IF(A11&lt;=360000,A11*0.2,IF(A11&lt;=1099999,A11*0.1,IF(A11&lt;=1999999,A11*0.08,IF(A11&lt;=6999999,A11*0.06,IF(A11&lt;=9999999,A11*0.04,A11*0.02))))))</f>
+        <f>IF(A11&lt;=1099999,MAX(A11*0.1,50000),IF(A11&lt;=1999999,A11*0.08,IF(A11&lt;=6999999,A11*0.06,IF(A11&lt;=9999999,A11*0.04,A11*0.02))))</f>
         <v/>
       </c>
       <c r="G11" s="6">
@@ -1351,7 +1307,7 @@
         <v/>
       </c>
       <c r="H11" s="6">
-        <f>G11*11</f>
+        <f>G11*12</f>
         <v/>
       </c>
     </row>

--- a/sletat-ru-mediaplan.xlsx
+++ b/sletat-ru-mediaplan.xlsx
@@ -61,7 +61,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -71,6 +71,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -438,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -452,6 +453,7 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -571,7 +573,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Расчёт по сегментам (бюджет делится поровну между сегментами)</t>
+          <t>Расчёт по сегментам (доли бюджета — жёлтая колонка L; основной сегмент — Ozon Travel)</t>
         </is>
       </c>
     </row>
@@ -631,6 +633,11 @@
           <t>Ёмкость: уникальных / мес</t>
         </is>
       </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Доля бюджета</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -639,7 +646,7 @@
         </is>
       </c>
       <c r="B16" s="6">
-        <f>$B$5/3</f>
+        <f>$B$5*L16</f>
         <v/>
       </c>
       <c r="C16" s="7" t="n">
@@ -675,6 +682,9 @@
       <c r="K16" s="6" t="n">
         <v>19458325</v>
       </c>
+      <c r="L16" s="9" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -683,7 +693,7 @@
         </is>
       </c>
       <c r="B17" s="6">
-        <f>$B$5/3</f>
+        <f>$B$5*L17</f>
         <v/>
       </c>
       <c r="C17" s="7" t="n">
@@ -719,6 +729,9 @@
       <c r="K17" s="6" t="n">
         <v>7191660</v>
       </c>
+      <c r="L17" s="9" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -727,7 +740,7 @@
         </is>
       </c>
       <c r="B18" s="6">
-        <f>$B$5/3</f>
+        <f>$B$5*L18</f>
         <v/>
       </c>
       <c r="C18" s="7" t="n">
@@ -763,6 +776,9 @@
       <c r="K18" s="6" t="n">
         <v>21646162</v>
       </c>
+      <c r="L18" s="9" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -770,7 +786,7 @@
           <t>Итого медиа Ozon Performance</t>
         </is>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="10">
         <f>SUM(B16:B18)</f>
         <v/>
       </c>
@@ -778,19 +794,19 @@
         <f>B19/E19*1000</f>
         <v/>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="11">
         <f>G19/E19</f>
         <v/>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="10">
         <f>SUM(E16:E18)</f>
         <v/>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="10">
         <f>SUM(F16:F18)</f>
         <v/>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="10">
         <f>SUM(G16:G18)</f>
         <v/>
       </c>
@@ -798,7 +814,7 @@
         <f>B19/G19</f>
         <v/>
       </c>
-      <c r="I19" s="9">
+      <c r="I19" s="10">
         <f>SUM(I16:I18)</f>
         <v/>
       </c>

--- a/sletat-ru-mediaplan.xlsx
+++ b/sletat-ru-mediaplan.xlsx
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>6999999</v>
